--- a/return_to_work_forms/004_fit_for_work_assessment_form--return_to_work_forms.xlsx
+++ b/return_to_work_forms/004_fit_for_work_assessment_form--return_to_work_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>return_to_work_forms_1</t>
+          <t>initial_assessment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Initial Assessment</t>
+          <t>How are you feeling today?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>return_to_work_forms_2</t>
+          <t>medical_report</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medical Report</t>
+          <t>Please describe your medical condition</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>return_to_work_forms_3</t>
+          <t>readiness</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Recommendations</t>
+          <t>Do you feel ready to return to work?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>return_to_work_forms_4</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Readiness</t>
+          <t>What are your recommendations?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>return_to_work_forms_5</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Recommendations</t>
+          <t>What are your next steps?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>return_to_work_forms_6</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Next Steps</t>
+          <t>Please provide your contact information</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>return_to_work_forms_7</t>
+          <t>date_of_return</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>When do you plan to return to work?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>return_to_work_forms_8</t>
+          <t>time_of_return</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>At what time do you plan to return to work?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>return_to_work_forms_9</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Is there anything else you would like to add?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>return_to_work_forms_10</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Do you need any support?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,40 +745,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>return_to_work_forms_11</t>
+          <t>frequency_of_work</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Recommendations</t>
+          <t>How frequently do you plan to work?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>return_to_work_forms_12</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Next Steps</t>
+          <t>What are your availability?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>return_to_work_forms_13</t>
+          <t>time_of_day</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>At what time do you prefer to work?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,21 +814,44 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>return_to_work_forms_14</t>
+          <t>duration</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>How long do you plan to work?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Is there anything else you'd like to add?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,204 +896,153 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>return_to_work_forms_11_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>return_to_work_forms_11_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>return_to_work_forms_11_choices</t>
+          <t>next_steps_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>return_to_work_forms_12_choices</t>
+          <t>frequency_of_work_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>return_to_work_forms_12_choices</t>
+          <t>frequency_of_work_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>return_to_work_forms_12_choices</t>
+          <t>frequency_of_work_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>return_to_work_forms_13_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01/01/2024</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>return_to_work_forms_13_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>return_to_work_forms_13_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01/03/2024</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01/03/2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>return_to_work_forms_14_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>return_to_work_forms_14_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>return_to_work_forms_14_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>600</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
